--- a/Categoría/RUN_Categoría.xlsx
+++ b/Categoría/RUN_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>0.4085295208781692</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>110.6984979308547</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.4584772227615653</v>
+        <v>0.4522360432162508</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -907,7 +907,7 @@
         <v>6</v>
       </c>
       <c r="E6" s="2">
-        <v>1.888514080626451</v>
+        <v>1.888514080626452</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1255,10 +1255,10 @@
         <v>31</v>
       </c>
       <c r="B27" s="2">
-        <v>0.5097302737961548</v>
+        <v>0.5097302737961549</v>
       </c>
       <c r="C27" s="2">
-        <v>107.8770429527525</v>
+        <v>107.8770429527524</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>6</v>
@@ -2020,7 +2020,7 @@
         <v>76</v>
       </c>
       <c r="B72" s="2">
-        <v>0.6352078125669371</v>
+        <v>0.635207812566937</v>
       </c>
       <c r="C72" s="2">
         <v>105.0434233047983</v>
@@ -2904,7 +2904,7 @@
         <v>128</v>
       </c>
       <c r="B124" s="2">
-        <v>5.90461661251293</v>
+        <v>5.904616612512929</v>
       </c>
       <c r="C124" s="2">
         <v>121.0959664956929</v>
@@ -2913,7 +2913,7 @@
         <v>6</v>
       </c>
       <c r="E124" s="2">
-        <v>7.150252554787775</v>
+        <v>7.150252554787774</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2924,7 +2924,7 @@
         <v>9.472264046341213</v>
       </c>
       <c r="C125" s="2">
-        <v>114.3235783899573</v>
+        <v>114.3235783899572</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>6</v>
